--- a/data/trans_orig/P16A13-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P16A13-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2783</t>
+          <t>2732</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14125</t>
+          <t>13630</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3038</t>
+          <t>2960</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14080</t>
+          <t>13619</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8552</t>
+          <t>7864</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24350</t>
+          <t>23651</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>258885</t>
+          <t>259380</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>270227</t>
+          <t>270278</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>246758</t>
+          <t>247219</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>257800</t>
+          <t>257878</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>509498</t>
+          <t>510197</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>525296</t>
+          <t>525984</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10366</t>
+          <t>10274</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26306</t>
+          <t>27393</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11975</t>
+          <t>12112</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28474</t>
+          <t>28058</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25811</t>
+          <t>25832</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51443</t>
+          <t>50979</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>466769</t>
+          <t>465682</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>482709</t>
+          <t>482801</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>475475</t>
+          <t>475891</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>491974</t>
+          <t>491837</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>945581</t>
+          <t>946045</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>971213</t>
+          <t>971192</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1916</t>
+          <t>1942</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10784</t>
+          <t>11500</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6475</t>
+          <t>6626</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20934</t>
+          <t>20482</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10351</t>
+          <t>10321</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26808</t>
+          <t>26423</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>308062</t>
+          <t>307346</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>316930</t>
+          <t>316904</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>314478</t>
+          <t>314930</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>328937</t>
+          <t>328786</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>627450</t>
+          <t>627835</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>643907</t>
+          <t>643937</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2944</t>
+          <t>2865</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14744</t>
+          <t>14291</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9853</t>
+          <t>9476</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24708</t>
+          <t>23716</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14837</t>
+          <t>15130</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33513</t>
+          <t>33504</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>343927</t>
+          <t>344380</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>355727</t>
+          <t>355806</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>346748</t>
+          <t>347740</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>361603</t>
+          <t>361980</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>696614</t>
+          <t>696623</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>715290</t>
+          <t>714997</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,93%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1604</t>
+          <t>894</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9888</t>
+          <t>9147</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3890</t>
+          <t>3935</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15222</t>
+          <t>16091</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6639</t>
+          <t>6568</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21115</t>
+          <t>20776</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>193420</t>
+          <t>194161</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>201704</t>
+          <t>202414</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>192446</t>
+          <t>191577</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>203778</t>
+          <t>203733</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>389861</t>
+          <t>390200</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>404337</t>
+          <t>404408</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1916</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11238</t>
+          <t>11013</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6295</t>
+          <t>6181</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20506</t>
+          <t>19767</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9686</t>
+          <t>10230</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26568</t>
+          <t>26254</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>259573</t>
+          <t>259798</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>268895</t>
+          <t>268879</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>257638</t>
+          <t>258377</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>271849</t>
+          <t>271963</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>522387</t>
+          <t>522701</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>539269</t>
+          <t>538725</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,14%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11480</t>
+          <t>11318</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30345</t>
+          <t>29170</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20948</t>
+          <t>20769</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>41585</t>
+          <t>42169</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>36446</t>
+          <t>36857</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>63895</t>
+          <t>63268</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>584682</t>
+          <t>585857</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>603547</t>
+          <t>603709</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>596634</t>
+          <t>596050</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>617271</t>
+          <t>617450</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1189351</t>
+          <t>1189978</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1216800</t>
+          <t>1216389</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,06%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13868</t>
+          <t>14258</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>32964</t>
+          <t>33855</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,82 +3149,82 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>4,56%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>17617</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>10381</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>26672</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>3,4%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>39945</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>28510</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>54379</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>2,62%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>1,87%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>4,44%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>17617</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>10807</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>28349</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>3,62%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>39945</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>28826</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>55328</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>2,62%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>709813</t>
+          <t>708922</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>728909</t>
+          <t>728519</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,82 +3262,82 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
+          <t>98,08%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>729</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>765894</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>756839</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>773130</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>97,75%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>96,6%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>98,68%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>1441</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>1486343</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>1471909</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>1497778</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>97,38%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>96,44%</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
           <t>98,13%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>729</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>765894</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>755162</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>772704</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>97,75%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>96,38%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>98,62%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>1441</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>1486343</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>1470960</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>1497462</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>97,38%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>96,37%</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>98,11%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>70617</t>
+          <t>70576</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>108614</t>
+          <t>106821</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>101921</t>
+          <t>101559</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>142388</t>
+          <t>142806</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>178837</t>
+          <t>181139</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>234861</t>
+          <t>237608</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3166911</t>
+          <t>3168704</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3204908</t>
+          <t>3204949</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3236809</t>
+          <t>3236391</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3277276</t>
+          <t>3277638</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6419861</t>
+          <t>6417114</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6475885</t>
+          <t>6473583</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,28%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas en 2012 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10668</t>
+          <t>10429</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30078</t>
+          <t>29488</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11289</t>
+          <t>11095</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28962</t>
+          <t>27943</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24990</t>
+          <t>26325</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>50224</t>
+          <t>51123</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,95%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>260125</t>
+          <t>260715</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>279535</t>
+          <t>279774</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>252318</t>
+          <t>253337</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>269991</t>
+          <t>270185</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>521259</t>
+          <t>520360</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>546493</t>
+          <t>545158</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,39%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17595</t>
+          <t>18079</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39627</t>
+          <t>38303</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22054</t>
+          <t>21576</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45854</t>
+          <t>45053</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43911</t>
+          <t>44860</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>75134</t>
+          <t>75842</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>465900</t>
+          <t>467224</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>487932</t>
+          <t>487448</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>476877</t>
+          <t>477678</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>500677</t>
+          <t>501155</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>953124</t>
+          <t>952416</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>984347</t>
+          <t>983398</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,64%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5046</t>
+          <t>6063</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22287</t>
+          <t>23103</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7203</t>
+          <t>7641</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21452</t>
+          <t>22364</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15870</t>
+          <t>16584</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37747</t>
+          <t>39154</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>300829</t>
+          <t>300013</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>318070</t>
+          <t>317053</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>319568</t>
+          <t>318656</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>333817</t>
+          <t>333379</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>626389</t>
+          <t>624982</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>648266</t>
+          <t>647552</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,5%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>3928</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17184</t>
+          <t>17216</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21237</t>
+          <t>21341</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42058</t>
+          <t>41931</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29114</t>
+          <t>27318</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53969</t>
+          <t>52626</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>356798</t>
+          <t>356766</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>370057</t>
+          <t>370054</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>345916</t>
+          <t>346043</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>366737</t>
+          <t>366633</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>707987</t>
+          <t>709330</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>732842</t>
+          <t>734638</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,41%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10570</t>
+          <t>10324</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27006</t>
+          <t>26343</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8702</t>
+          <t>9265</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25136</t>
+          <t>24901</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21695</t>
+          <t>22690</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46183</t>
+          <t>46551</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,77%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>185612</t>
+          <t>186275</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>202048</t>
+          <t>202294</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>194455</t>
+          <t>194690</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>210889</t>
+          <t>210326</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>386026</t>
+          <t>385658</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>410514</t>
+          <t>409519</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,75%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8443</t>
+          <t>7805</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24614</t>
+          <t>23725</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,82 +5786,82 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
+          <t>2,85%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>8,66%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>10845</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>5818</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>18833</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>3,89%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>6,75%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>25065</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>17029</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>37299</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>4,53%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
           <t>3,08%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>8,98%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>10845</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>5909</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>18740</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>3,89%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>6,71%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>25065</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>16491</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>37238</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>4,53%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>2,98%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>249367</t>
+          <t>250256</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265538</t>
+          <t>266176</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,82 +5899,82 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>97,15%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>268295</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>260307</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>273322</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>96,11%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>93,25%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>97,92%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>505</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>528056</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>515822</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>536092</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>95,47%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>93,26%</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
           <t>96,92%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>268295</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>260400</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>273231</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>96,11%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>93,29%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>97,88%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>505</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>528056</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>515883</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>536630</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>95,47%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>93,27%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>97,02%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13989</t>
+          <t>14758</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>34839</t>
+          <t>34894</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>25680</t>
+          <t>25488</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>51774</t>
+          <t>51526</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>45116</t>
+          <t>44423</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>78800</t>
+          <t>79063</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>625676</t>
+          <t>625621</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>646526</t>
+          <t>645757</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>642079</t>
+          <t>642327</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>668173</t>
+          <t>668365</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1275568</t>
+          <t>1275305</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1309252</t>
+          <t>1309945</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,72%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11869</t>
+          <t>12131</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>31231</t>
+          <t>31946</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>23254</t>
+          <t>22534</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>47485</t>
+          <t>46204</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>40068</t>
+          <t>38242</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>71693</t>
+          <t>69799</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>744650</t>
+          <t>743935</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>764012</t>
+          <t>763750</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>774035</t>
+          <t>775316</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>798266</t>
+          <t>798986</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1525709</t>
+          <t>1527603</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1557334</t>
+          <t>1559160</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>114170</t>
+          <t>117282</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>166447</t>
+          <t>167490</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>163853</t>
+          <t>162886</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>220822</t>
+          <t>219087</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>295469</t>
+          <t>296390</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>369878</t>
+          <t>368209</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3249378</t>
+          <t>3248335</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3301655</t>
+          <t>3298543</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3326288</t>
+          <t>3328023</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3383257</t>
+          <t>3384224</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6593056</t>
+          <t>6594725</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6667465</t>
+          <t>6666544</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,74%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>3996</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15143</t>
+          <t>15273</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14773</t>
+          <t>13759</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34070</t>
+          <t>35326</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22150</t>
+          <t>22659</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44837</t>
+          <t>45845</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>278618</t>
+          <t>278488</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>289815</t>
+          <t>289765</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>254633</t>
+          <t>253377</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>273930</t>
+          <t>274944</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>537627</t>
+          <t>536619</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>560314</t>
+          <t>559805</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,11%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5882</t>
+          <t>5907</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19902</t>
+          <t>19305</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,82 +7737,82 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,84%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>8574</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>3986</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>16732</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>19722</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>12037</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>31427</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>1,17%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,96%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>8574</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>3969</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>16513</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>3,16%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>19722</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>10783</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>29528</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>482673</t>
+          <t>483270</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>496693</t>
+          <t>496668</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,82 +7850,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>98,82%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>476</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>514510</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>506352</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>519098</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>98,36%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>96,8%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>99,24%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1005937</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>994232</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>1013622</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>98,08%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>96,94%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>98,83%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>476</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>514510</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>506571</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>519115</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,36%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>96,84%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,24%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1005937</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>996131</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1014876</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>98,08%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>97,12%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2775</t>
+          <t>2057</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12870</t>
+          <t>12537</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2636</t>
+          <t>2361</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12155</t>
+          <t>13431</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6567</t>
+          <t>7209</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20633</t>
+          <t>21235</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>305695</t>
+          <t>306028</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>315790</t>
+          <t>316508</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>324154</t>
+          <t>322878</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>333673</t>
+          <t>333948</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>634241</t>
+          <t>633639</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>648307</t>
+          <t>647665</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9888</t>
+          <t>10108</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26734</t>
+          <t>27681</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19706</t>
+          <t>19023</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43414</t>
+          <t>44068</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34057</t>
+          <t>33612</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>61751</t>
+          <t>62581</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>343230</t>
+          <t>342283</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>360076</t>
+          <t>359856</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>343869</t>
+          <t>343215</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>367577</t>
+          <t>368260</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>695496</t>
+          <t>694666</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>723190</t>
+          <t>723635</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,56%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>948</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8611</t>
+          <t>8963</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2983</t>
+          <t>2972</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14266</t>
+          <t>14275</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5126</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19189</t>
+          <t>17582</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>202610</t>
+          <t>202258</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>210280</t>
+          <t>210273</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>204321</t>
+          <t>204312</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>215604</t>
+          <t>215615</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>410619</t>
+          <t>412226</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>424682</t>
+          <t>424583</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,78%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4253</t>
+          <t>3942</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15435</t>
+          <t>14840</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,82 +9109,82 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>5,64%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>6520</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>2472</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>13255</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>4,85%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>14830</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>8673</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>24205</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>2,77%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
           <t>1,62%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>5,87%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>6520</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>2847</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>14771</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>5,41%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>14830</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>8805</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>24561</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>2,77%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>247688</t>
+          <t>248283</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>258870</t>
+          <t>259181</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,82 +9222,82 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>98,5%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>266595</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>259860</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>270643</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>97,61%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>95,15%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>99,09%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>507</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>521408</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>512033</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>527565</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>97,23%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>95,49%</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
           <t>98,38%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>266595</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>258344</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>270268</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>97,61%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>94,59%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>98,96%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>507</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>521408</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>511677</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>527433</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>97,23%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>95,42%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>98,36%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16118</t>
+          <t>16050</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>37291</t>
+          <t>38678</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23157</t>
+          <t>23479</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>49083</t>
+          <t>48960</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>44365</t>
+          <t>44073</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>77948</t>
+          <t>77149</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>619267</t>
+          <t>617880</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>640440</t>
+          <t>640508</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>642211</t>
+          <t>642334</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>668137</t>
+          <t>667815</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1269904</t>
+          <t>1270703</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1303487</t>
+          <t>1303779</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,73%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12857</t>
+          <t>12404</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>32447</t>
+          <t>33058</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>18655</t>
+          <t>17777</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>40151</t>
+          <t>40602</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>34885</t>
+          <t>35807</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>63153</t>
+          <t>65826</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>746136</t>
+          <t>745525</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>765726</t>
+          <t>766179</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>786016</t>
+          <t>785565</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>807512</t>
+          <t>808390</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1541597</t>
+          <t>1538924</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1569865</t>
+          <t>1568943</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>81052</t>
+          <t>80122</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>122688</t>
+          <t>121868</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>119777</t>
+          <t>121848</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>171144</t>
+          <t>171702</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>213981</t>
+          <t>211384</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>276229</t>
+          <t>277284</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3271662</t>
+          <t>3272482</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3313298</t>
+          <t>3314228</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3373398</t>
+          <t>3372840</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3424765</t>
+          <t>3422694</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6662663</t>
+          <t>6661608</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6724911</t>
+          <t>6727508</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,95%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas en 2023 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11247</t>
+          <t>11708</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39571</t>
+          <t>44663</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8898</t>
+          <t>8873</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19424</t>
+          <t>19534</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23190</t>
+          <t>22659</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53717</t>
+          <t>51264</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>271872</t>
+          <t>266780</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>300196</t>
+          <t>299735</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>270211</t>
+          <t>270101</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>280737</t>
+          <t>280762</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>547360</t>
+          <t>549813</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>577887</t>
+          <t>578418</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,23%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6406</t>
+          <t>6249</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22911</t>
+          <t>22931</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,7 +11060,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11191</t>
+          <t>10754</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25210</t>
+          <t>25033</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21263</t>
+          <t>21081</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>42688</t>
+          <t>42421</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>494482</t>
+          <t>494462</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>510987</t>
+          <t>511144</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11178,7 +11178,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>488515</t>
+          <t>488692</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>502534</t>
+          <t>502971</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>988430</t>
+          <t>988697</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1009855</t>
+          <t>1010037</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,96%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24933</t>
+          <t>24908</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43005</t>
+          <t>43264</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46775</t>
+          <t>46095</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>66443</t>
+          <t>66675</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>75750</t>
+          <t>74688</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>104935</t>
+          <t>104127</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,65%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>273045</t>
+          <t>272786</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>291117</t>
+          <t>291142</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>282685</t>
+          <t>282453</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>302353</t>
+          <t>303033</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>560243</t>
+          <t>561051</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>589428</t>
+          <t>590490</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,77%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12719</t>
+          <t>12926</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29546</t>
+          <t>28129</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22947</t>
+          <t>23504</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50509</t>
+          <t>51111</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41111</t>
+          <t>39913</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>72276</t>
+          <t>72934</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,25%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>283011</t>
+          <t>284428</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>299838</t>
+          <t>299631</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>425209</t>
+          <t>424607</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>452771</t>
+          <t>452214</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>715998</t>
+          <t>715340</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>747163</t>
+          <t>748361</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,94%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17599</t>
+          <t>17390</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30950</t>
+          <t>31788</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37418</t>
+          <t>37130</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51980</t>
+          <t>51852</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>57733</t>
+          <t>57847</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>78773</t>
+          <t>78347</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,22%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>147792</t>
+          <t>146954</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>161143</t>
+          <t>161352</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>156676</t>
+          <t>156804</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>171238</t>
+          <t>171526</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>308625</t>
+          <t>309051</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>329665</t>
+          <t>329551</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>85,07%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29967</t>
+          <t>30076</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>46452</t>
+          <t>47240</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>33331</t>
+          <t>33501</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>48694</t>
+          <t>49711</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>66292</t>
+          <t>67242</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>91406</t>
+          <t>91612</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,39%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>223184</t>
+          <t>222396</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>239669</t>
+          <t>239560</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>208362</t>
+          <t>207345</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>223725</t>
+          <t>223555</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>435286</t>
+          <t>435080</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>460400</t>
+          <t>459450</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,23%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25787</t>
+          <t>25509</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>49526</t>
+          <t>48122</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28421</t>
+          <t>26698</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>77014</t>
+          <t>76670</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>55882</t>
+          <t>56135</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>112973</t>
+          <t>113889</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>574753</t>
+          <t>576157</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>598492</t>
+          <t>598770</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>772251</t>
+          <t>772595</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>820844</t>
+          <t>822567</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1360571</t>
+          <t>1359655</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1417662</t>
+          <t>1417409</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,19%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10794</t>
+          <t>9349</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>39710</t>
+          <t>38828</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>16061</t>
+          <t>14800</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>29587</t>
+          <t>29425</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>28737</t>
+          <t>27626</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>61356</t>
+          <t>62169</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>889010</t>
+          <t>889892</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>917926</t>
+          <t>919371</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>685264</t>
+          <t>685426</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>698790</t>
+          <t>700051</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1582216</t>
+          <t>1581403</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1614835</t>
+          <t>1615946</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,32%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>164059</t>
+          <t>157256</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>241010</t>
+          <t>239591</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>231207</t>
+          <t>235759</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>317937</t>
+          <t>319722</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>430868</t>
+          <t>428459</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>543050</t>
+          <t>539202</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3217810</t>
+          <t>3219229</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3294761</t>
+          <t>3301564</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3340096</t>
+          <t>3338311</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3426826</t>
+          <t>3422274</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6573803</t>
+          <t>6577651</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6685985</t>
+          <t>6688394</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,98%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A13-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P16A13-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2732</t>
+          <t>2778</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13630</t>
+          <t>13444</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2960</t>
+          <t>3158</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13619</t>
+          <t>15051</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7864</t>
+          <t>8550</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23651</t>
+          <t>23987</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>259380</t>
+          <t>259566</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>270278</t>
+          <t>270232</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>247219</t>
+          <t>245787</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>257878</t>
+          <t>257680</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>510197</t>
+          <t>509861</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>525984</t>
+          <t>525298</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10274</t>
+          <t>9152</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27393</t>
+          <t>26100</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12112</t>
+          <t>12266</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28058</t>
+          <t>29498</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25832</t>
+          <t>25848</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50979</t>
+          <t>48371</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>465682</t>
+          <t>466975</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>482801</t>
+          <t>483923</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>475891</t>
+          <t>474451</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>491837</t>
+          <t>491683</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>946045</t>
+          <t>948653</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>971192</t>
+          <t>971176</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1942</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11500</t>
+          <t>10673</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6626</t>
+          <t>7061</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20482</t>
+          <t>21438</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10321</t>
+          <t>10057</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26423</t>
+          <t>27072</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>307346</t>
+          <t>308173</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>316904</t>
+          <t>316912</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>314930</t>
+          <t>313974</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>328786</t>
+          <t>328351</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>627835</t>
+          <t>627186</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>643937</t>
+          <t>644201</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,46%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2865</t>
+          <t>2959</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14291</t>
+          <t>14964</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9476</t>
+          <t>9356</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23716</t>
+          <t>24084</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15130</t>
+          <t>15153</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33504</t>
+          <t>33537</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>344380</t>
+          <t>343707</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>355806</t>
+          <t>355712</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>347740</t>
+          <t>347372</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>361980</t>
+          <t>362100</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>696623</t>
+          <t>696590</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>714997</t>
+          <t>714974</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,92%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>910</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9147</t>
+          <t>9254</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3935</t>
+          <t>3694</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16091</t>
+          <t>16129</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6568</t>
+          <t>6466</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20776</t>
+          <t>19944</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>194161</t>
+          <t>194054</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>202414</t>
+          <t>202398</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>191577</t>
+          <t>191539</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>203733</t>
+          <t>203974</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>390200</t>
+          <t>391032</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>404408</t>
+          <t>404510</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,43%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1932</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11013</t>
+          <t>11981</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6181</t>
+          <t>6195</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19767</t>
+          <t>20358</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10230</t>
+          <t>9485</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26254</t>
+          <t>26360</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>259798</t>
+          <t>258830</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>268879</t>
+          <t>268810</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>258377</t>
+          <t>257786</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>271963</t>
+          <t>271949</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>522701</t>
+          <t>522595</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>538725</t>
+          <t>539470</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11318</t>
+          <t>11560</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29170</t>
+          <t>30797</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20769</t>
+          <t>19370</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>42169</t>
+          <t>39916</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>36857</t>
+          <t>36532</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>63268</t>
+          <t>64056</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>585857</t>
+          <t>584230</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>603709</t>
+          <t>603467</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>596050</t>
+          <t>598303</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>617450</t>
+          <t>618849</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1189978</t>
+          <t>1189190</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1216389</t>
+          <t>1216714</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,09%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14258</t>
+          <t>13826</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>33855</t>
+          <t>31817</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10381</t>
+          <t>10189</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26672</t>
+          <t>27824</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>28510</t>
+          <t>29029</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>54379</t>
+          <t>53415</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>708922</t>
+          <t>710960</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>728519</t>
+          <t>728951</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>756839</t>
+          <t>755687</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>773130</t>
+          <t>773322</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1471909</t>
+          <t>1472873</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1497778</t>
+          <t>1497259</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,1%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>70576</t>
+          <t>70173</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>106821</t>
+          <t>105971</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>101559</t>
+          <t>102113</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>142806</t>
+          <t>142944</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>182237</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>237608</t>
+          <t>239500</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3168704</t>
+          <t>3169554</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3204949</t>
+          <t>3205352</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3236391</t>
+          <t>3236253</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3277638</t>
+          <t>3277084</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6417114</t>
+          <t>6415222</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6473583</t>
+          <t>6472485</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,26%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10429</t>
+          <t>10060</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29488</t>
+          <t>29563</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11095</t>
+          <t>11502</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27943</t>
+          <t>30140</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26325</t>
+          <t>24820</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51123</t>
+          <t>50335</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>260715</t>
+          <t>260640</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>279774</t>
+          <t>280143</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>253337</t>
+          <t>251140</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>270185</t>
+          <t>269778</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>520360</t>
+          <t>521148</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>545158</t>
+          <t>546663</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,66%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18079</t>
+          <t>18382</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38303</t>
+          <t>39255</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21576</t>
+          <t>21677</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45053</t>
+          <t>43003</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44860</t>
+          <t>44123</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>75842</t>
+          <t>75210</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>467224</t>
+          <t>466272</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>487448</t>
+          <t>487145</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>477678</t>
+          <t>479728</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>501155</t>
+          <t>501054</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>952416</t>
+          <t>953048</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>983398</t>
+          <t>984135</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,71%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6063</t>
+          <t>5459</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23103</t>
+          <t>22654</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7641</t>
+          <t>7523</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22364</t>
+          <t>22270</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16584</t>
+          <t>16916</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39154</t>
+          <t>38118</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>300013</t>
+          <t>300462</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>317053</t>
+          <t>317657</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>318656</t>
+          <t>318750</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>333379</t>
+          <t>333497</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>624982</t>
+          <t>626018</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>647552</t>
+          <t>647220</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,45%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3928</t>
+          <t>3929</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17216</t>
+          <t>17410</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21341</t>
+          <t>20720</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41931</t>
+          <t>42451</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27318</t>
+          <t>27557</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>52626</t>
+          <t>53896</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>356766</t>
+          <t>356572</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>370054</t>
+          <t>370053</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>346043</t>
+          <t>345523</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>366633</t>
+          <t>367254</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>709330</t>
+          <t>708060</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>734638</t>
+          <t>734399</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,38%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10324</t>
+          <t>9680</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26343</t>
+          <t>25649</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9265</t>
+          <t>8716</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24901</t>
+          <t>23778</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22690</t>
+          <t>21443</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46551</t>
+          <t>44411</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>186275</t>
+          <t>186969</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>202294</t>
+          <t>202938</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>194690</t>
+          <t>195813</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>210326</t>
+          <t>210875</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>385658</t>
+          <t>387798</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>409519</t>
+          <t>410766</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>95,04%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7805</t>
+          <t>8201</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23725</t>
+          <t>24493</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5818</t>
+          <t>5115</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18833</t>
+          <t>18014</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17029</t>
+          <t>16903</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>37299</t>
+          <t>36095</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>250256</t>
+          <t>249488</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266176</t>
+          <t>265780</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>260307</t>
+          <t>261126</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>273322</t>
+          <t>274025</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>515822</t>
+          <t>517026</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>536092</t>
+          <t>536218</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,94%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14758</t>
+          <t>14771</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>34894</t>
+          <t>35987</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>25488</t>
+          <t>26274</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>51526</t>
+          <t>52294</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>44423</t>
+          <t>43782</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>79063</t>
+          <t>76892</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>625621</t>
+          <t>624528</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>645757</t>
+          <t>645744</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>642327</t>
+          <t>641559</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>668365</t>
+          <t>667579</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1275305</t>
+          <t>1277476</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1309945</t>
+          <t>1310586</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,77%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12131</t>
+          <t>11614</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>31946</t>
+          <t>31058</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>22534</t>
+          <t>22520</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>46204</t>
+          <t>46903</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>38242</t>
+          <t>40362</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>69799</t>
+          <t>70855</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>743935</t>
+          <t>744823</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>763750</t>
+          <t>764267</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>775316</t>
+          <t>774617</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>798986</t>
+          <t>799000</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1527603</t>
+          <t>1526547</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1559160</t>
+          <t>1557040</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,47%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>117282</t>
+          <t>116213</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>167490</t>
+          <t>165627</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>162886</t>
+          <t>165743</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>219087</t>
+          <t>220736</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>296390</t>
+          <t>294840</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>368209</t>
+          <t>368516</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3248335</t>
+          <t>3250198</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3298543</t>
+          <t>3299612</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3328023</t>
+          <t>3326374</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3384224</t>
+          <t>3381367</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6594725</t>
+          <t>6594418</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6666544</t>
+          <t>6668094</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,77%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3996</t>
+          <t>4561</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15273</t>
+          <t>16841</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13759</t>
+          <t>15256</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35326</t>
+          <t>35182</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22659</t>
+          <t>22335</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45845</t>
+          <t>46364</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>278488</t>
+          <t>276920</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>289765</t>
+          <t>289200</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>253377</t>
+          <t>253521</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>274944</t>
+          <t>273447</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>536619</t>
+          <t>536100</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>559805</t>
+          <t>560129</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,17%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5907</t>
+          <t>5801</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19305</t>
+          <t>20001</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3986</t>
+          <t>3954</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16732</t>
+          <t>16696</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12037</t>
+          <t>11576</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31427</t>
+          <t>30180</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>483270</t>
+          <t>482574</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>496668</t>
+          <t>496774</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>506352</t>
+          <t>506388</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>519098</t>
+          <t>519130</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>994232</t>
+          <t>995479</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1013622</t>
+          <t>1014083</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2057</t>
+          <t>2220</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12537</t>
+          <t>13036</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2361</t>
+          <t>2794</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13431</t>
+          <t>13598</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7209</t>
+          <t>7261</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21235</t>
+          <t>20963</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>306028</t>
+          <t>305529</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>316508</t>
+          <t>316345</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>322878</t>
+          <t>322711</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>333948</t>
+          <t>333515</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>633639</t>
+          <t>633911</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>647665</t>
+          <t>647613</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,89%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10108</t>
+          <t>9983</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27681</t>
+          <t>26794</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19023</t>
+          <t>19235</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44068</t>
+          <t>43017</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33612</t>
+          <t>33146</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>62581</t>
+          <t>62749</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>342283</t>
+          <t>343170</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>359856</t>
+          <t>359981</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>343215</t>
+          <t>344266</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>368260</t>
+          <t>368048</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>694666</t>
+          <t>694498</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>723635</t>
+          <t>724101</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,62%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>937</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8963</t>
+          <t>8912</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14275</t>
+          <t>13455</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>4935</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17582</t>
+          <t>17229</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>202258</t>
+          <t>202309</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>210273</t>
+          <t>210284</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,7 +8899,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>204312</t>
+          <t>205132</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>412226</t>
+          <t>412579</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>424583</t>
+          <t>424873</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3942</t>
+          <t>4355</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14840</t>
+          <t>15334</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13255</t>
+          <t>13739</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8673</t>
+          <t>8967</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24205</t>
+          <t>23580</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>248283</t>
+          <t>247789</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>259181</t>
+          <t>258768</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>259860</t>
+          <t>259376</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>270643</t>
+          <t>270661</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>512033</t>
+          <t>512658</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>527565</t>
+          <t>527271</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,33%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16050</t>
+          <t>16070</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38678</t>
+          <t>36712</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23479</t>
+          <t>24258</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>48960</t>
+          <t>49516</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>44073</t>
+          <t>45606</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>77149</t>
+          <t>76778</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>617880</t>
+          <t>619846</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>640508</t>
+          <t>640488</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>642334</t>
+          <t>641778</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>667815</t>
+          <t>667036</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1270703</t>
+          <t>1271074</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1303779</t>
+          <t>1302246</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,62%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12404</t>
+          <t>12704</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>33058</t>
+          <t>33795</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>17777</t>
+          <t>17773</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>40602</t>
+          <t>40560</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>35807</t>
+          <t>34097</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>65826</t>
+          <t>64806</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>745525</t>
+          <t>744788</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>766179</t>
+          <t>765879</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>785565</t>
+          <t>785607</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>808390</t>
+          <t>808394</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1538924</t>
+          <t>1539944</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1568943</t>
+          <t>1570653</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,88%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>80122</t>
+          <t>82159</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>121868</t>
+          <t>123631</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>121848</t>
+          <t>119203</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>171702</t>
+          <t>171138</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>211384</t>
+          <t>213192</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>277284</t>
+          <t>277135</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3272482</t>
+          <t>3270719</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3314228</t>
+          <t>3312191</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3372840</t>
+          <t>3373404</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3422694</t>
+          <t>3425339</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6661608</t>
+          <t>6661757</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6727508</t>
+          <t>6725700</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,93%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>19561</t>
+          <t>16529</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11708</t>
+          <t>10181</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44663</t>
+          <t>27642</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>13311</t>
+          <t>13547</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8873</t>
+          <t>8638</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19534</t>
+          <t>19186</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>32872</t>
+          <t>30076</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22659</t>
+          <t>21566</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51264</t>
+          <t>42489</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>6,69%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>291882</t>
+          <t>302316</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>266780</t>
+          <t>291203</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>299735</t>
+          <t>308664</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>276324</t>
+          <t>302514</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>270101</t>
+          <t>296875</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>280762</t>
+          <t>307423</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>568205</t>
+          <t>604830</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>549813</t>
+          <t>592417</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>578418</t>
+          <t>613340</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,6%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13343</t>
+          <t>13388</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6249</t>
+          <t>6776</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22931</t>
+          <t>22922</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17243</t>
+          <t>17648</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10754</t>
+          <t>11334</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25033</t>
+          <t>25467</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>30585</t>
+          <t>31035</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21081</t>
+          <t>21323</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>42421</t>
+          <t>42763</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>504050</t>
+          <t>516272</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>494462</t>
+          <t>506738</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>511144</t>
+          <t>522884</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>496482</t>
+          <t>527565</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>488692</t>
+          <t>519746</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>502971</t>
+          <t>533879</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1000533</t>
+          <t>1043838</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>988697</t>
+          <t>1032110</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1010037</t>
+          <t>1053550</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,02%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>513725</t>
+          <t>545213</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>513725</t>
+          <t>545213</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>513725</t>
+          <t>545213</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1031118</t>
+          <t>1074873</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1031118</t>
+          <t>1074873</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1031118</t>
+          <t>1074873</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>33349</t>
+          <t>34017</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24908</t>
+          <t>25650</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43264</t>
+          <t>46279</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>55964</t>
+          <t>58456</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46095</t>
+          <t>48509</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>66675</t>
+          <t>70019</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>89313</t>
+          <t>92474</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>74688</t>
+          <t>78190</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>104127</t>
+          <t>108213</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>16,09%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>282701</t>
+          <t>281976</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>272786</t>
+          <t>269714</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>291142</t>
+          <t>290343</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>293164</t>
+          <t>297925</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>282453</t>
+          <t>286362</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>303033</t>
+          <t>307872</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>575865</t>
+          <t>579901</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>561051</t>
+          <t>564162</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>590490</t>
+          <t>594185</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,37%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19349</t>
+          <t>23514</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12926</t>
+          <t>15322</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28129</t>
+          <t>33793</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>37835</t>
+          <t>41477</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23504</t>
+          <t>32099</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51111</t>
+          <t>51468</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>57184</t>
+          <t>64991</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39913</t>
+          <t>52354</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>72934</t>
+          <t>78350</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,85%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>293208</t>
+          <t>349631</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>284428</t>
+          <t>339352</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>299631</t>
+          <t>357823</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>437883</t>
+          <t>380484</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>424607</t>
+          <t>370493</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>452214</t>
+          <t>389862</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>731090</t>
+          <t>730116</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>715340</t>
+          <t>716757</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>748361</t>
+          <t>742753</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>93,42%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>24002</t>
+          <t>25722</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17390</t>
+          <t>19311</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31788</t>
+          <t>33290</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>43915</t>
+          <t>45620</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37130</t>
+          <t>38142</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51852</t>
+          <t>53348</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>67917</t>
+          <t>71342</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>57847</t>
+          <t>61797</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>78347</t>
+          <t>82072</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>18,96%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>154740</t>
+          <t>179943</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>146954</t>
+          <t>172375</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>161352</t>
+          <t>186354</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>164741</t>
+          <t>181595</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>156804</t>
+          <t>173867</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>171526</t>
+          <t>189073</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>79,92%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>319481</t>
+          <t>361537</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>309051</t>
+          <t>350807</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>329551</t>
+          <t>371082</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>81,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>85,72%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>37528</t>
+          <t>36949</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30076</t>
+          <t>29017</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>47240</t>
+          <t>47125</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>40863</t>
+          <t>41796</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>33501</t>
+          <t>34127</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>49711</t>
+          <t>51160</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>78390</t>
+          <t>78746</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>67242</t>
+          <t>67912</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>91612</t>
+          <t>91483</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,12%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>232108</t>
+          <t>233758</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>222396</t>
+          <t>223582</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>239560</t>
+          <t>241690</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>216193</t>
+          <t>221954</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>207345</t>
+          <t>212590</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>223555</t>
+          <t>229623</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>448302</t>
+          <t>455711</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>435080</t>
+          <t>442974</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>459450</t>
+          <t>466545</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,29%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>35874</t>
+          <t>42305</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25509</t>
+          <t>30519</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>48122</t>
+          <t>56597</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>55324</t>
+          <t>68706</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>26698</t>
+          <t>56023</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>76670</t>
+          <t>83358</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>91198</t>
+          <t>111011</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>56135</t>
+          <t>93657</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>113889</t>
+          <t>130833</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>588405</t>
+          <t>677382</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>576157</t>
+          <t>663090</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>598770</t>
+          <t>689168</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>793941</t>
+          <t>703351</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>772595</t>
+          <t>688699</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>822567</t>
+          <t>716034</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1382346</t>
+          <t>1380733</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1359655</t>
+          <t>1360911</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1417409</t>
+          <t>1398087</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>93,72%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>25120</t>
+          <t>27949</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9349</t>
+          <t>18978</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>38828</t>
+          <t>38691</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>22057</t>
+          <t>25469</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14800</t>
+          <t>18576</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>29425</t>
+          <t>33551</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>47177</t>
+          <t>53418</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>27626</t>
+          <t>42438</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>62169</t>
+          <t>67165</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>903600</t>
+          <t>770123</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>889892</t>
+          <t>759381</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>919371</t>
+          <t>779094</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>692794</t>
+          <t>804537</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>685426</t>
+          <t>796455</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>700051</t>
+          <t>811430</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1596395</t>
+          <t>1574660</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1581403</t>
+          <t>1560913</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1615946</t>
+          <t>1585640</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>97,39%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>714851</t>
+          <t>830006</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>714851</t>
+          <t>830006</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>714851</t>
+          <t>830006</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1643572</t>
+          <t>1628078</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1643572</t>
+          <t>1628078</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1643572</t>
+          <t>1628078</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>208125</t>
+          <t>220373</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>157256</t>
+          <t>193771</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>239591</t>
+          <t>249185</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>286511</t>
+          <t>312720</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>235759</t>
+          <t>285399</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>319722</t>
+          <t>338445</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>494636</t>
+          <t>533093</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>428459</t>
+          <t>493532</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>539202</t>
+          <t>573701</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3250695</t>
+          <t>3311402</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3219229</t>
+          <t>3282590</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3301564</t>
+          <t>3338004</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3371522</t>
+          <t>3419925</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3338311</t>
+          <t>3394200</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3422274</t>
+          <t>3447246</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6622217</t>
+          <t>6731326</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6577651</t>
+          <t>6690718</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6688394</t>
+          <t>6770887</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,21%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3658033</t>
+          <t>3732645</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3658033</t>
+          <t>3732645</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3658033</t>
+          <t>3732645</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7116853</t>
+          <t>7264419</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7116853</t>
+          <t>7264419</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7116853</t>
+          <t>7264419</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
